--- a/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41481</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51552</t>
+          <t>52278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73787</t>
+          <t>74027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68483</t>
+          <t>67535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82402</t>
+          <t>82694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76808</t>
+          <t>76407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92340</t>
+          <t>93051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149712</t>
+          <t>149472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171947</t>
+          <t>171221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50503</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67501</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91253</t>
+          <t>90371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79282</t>
+          <t>79995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94926</t>
+          <t>94989</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90239</t>
+          <t>90666</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107364</t>
+          <t>107675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174454</t>
+          <t>175336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198206</t>
+          <t>198121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26877</t>
+          <t>27803</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55540</t>
+          <t>56655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76699</t>
+          <t>77428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69305</t>
+          <t>68612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83260</t>
+          <t>82919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70197</t>
+          <t>69633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85696</t>
+          <t>84770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143721</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164880</t>
+          <t>163765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50499</t>
+          <t>49505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72227</t>
+          <t>70963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42361</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60700</t>
+          <t>61083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98137</t>
+          <t>97948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125779</t>
+          <t>127826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93109</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114837</t>
+          <t>115831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96246</t>
+          <t>95863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>114945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196503</t>
+          <t>194456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224145</t>
+          <t>224334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141510</t>
+          <t>143346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176257</t>
+          <t>175521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141508</t>
+          <t>145465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176911</t>
+          <t>180130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294665</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343019</t>
+          <t>343331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327102</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361849</t>
+          <t>360013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>351638</t>
+          <t>348419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>383084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688889</t>
+          <t>688577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737243</t>
+          <t>736872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73084</t>
+          <t>72833</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85498</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92666</t>
+          <t>92607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103765</t>
+          <t>103834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169228</t>
+          <t>168700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186688</t>
+          <t>186267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24045</t>
+          <t>24296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39771</t>
+          <t>40299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98637</t>
+          <t>98474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112853</t>
+          <t>113157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116627</t>
+          <t>116961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132811</t>
+          <t>132189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219667</t>
+          <t>221725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241573</t>
+          <t>242317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37929</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>41222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63872</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81450</t>
+          <t>81427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93610</t>
+          <t>93161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>107073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181088</t>
+          <t>179545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>197218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>23424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21635</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>42089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111153</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126531</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114261</t>
+          <t>115268</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131332</t>
+          <t>131117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231242</t>
+          <t>231827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254216</t>
+          <t>254307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34849</t>
+          <t>34881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40680</t>
+          <t>39673</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46727</t>
+          <t>46636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69701</t>
+          <t>69116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>379315</t>
+          <t>380002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>407294</t>
+          <t>407906</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>433225</t>
+          <t>436171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>461879</t>
+          <t>462974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>824703</t>
+          <t>822566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>862665</t>
+          <t>861399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69671</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>96963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>75177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104926</t>
+          <t>101980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152450</t>
+          <t>153716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190412</t>
+          <t>192549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>54040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67835</t>
+          <t>68227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68022</t>
+          <t>67472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83429</t>
+          <t>83382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127344</t>
+          <t>128183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148298</t>
+          <t>147422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33278</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33774</t>
+          <t>34324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61669</t>
+          <t>60830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95462</t>
+          <t>95208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113699</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126656</t>
+          <t>126332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143140</t>
+          <t>143079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227286</t>
+          <t>226948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252217</t>
+          <t>252883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>36106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53972</t>
+          <t>54226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46506</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>69713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95310</t>
+          <t>95648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55417</t>
+          <t>54816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71967</t>
+          <t>71486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60348</t>
+          <t>60115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79070</t>
+          <t>78904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121527</t>
+          <t>121300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146548</t>
+          <t>144959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>42558</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58627</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52390</t>
+          <t>52556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71112</t>
+          <t>71345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98956</t>
+          <t>100545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123977</t>
+          <t>124204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110832</t>
+          <t>111227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>130639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99423</t>
+          <t>99791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117970</t>
+          <t>118350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214909</t>
+          <t>217730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244122</t>
+          <t>244657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>34690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>54102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37343</t>
+          <t>36963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55890</t>
+          <t>55522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76521</t>
+          <t>75986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>102913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>332904</t>
+          <t>334612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>368716</t>
+          <t>370677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>372009</t>
+          <t>373103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>409489</t>
+          <t>409824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>717982</t>
+          <t>718387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>767086</t>
+          <t>767403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147309</t>
+          <t>145348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183121</t>
+          <t>181413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152242</t>
+          <t>151907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189722</t>
+          <t>188628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>310353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359774</t>
+          <t>359369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32630</t>
+          <t>31886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48933</t>
+          <t>49230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40203</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72070</t>
+          <t>73718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77506</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117087</t>
+          <t>115529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67968</t>
+          <t>67671</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84271</t>
+          <t>85015</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>66694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100209</t>
+          <t>100760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140226</t>
+          <t>141784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179807</t>
+          <t>178610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61647</t>
+          <t>61324</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87055</t>
+          <t>87340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99577</t>
+          <t>99303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129179</t>
+          <t>130509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167596</t>
+          <t>168032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205454</t>
+          <t>207118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>100956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126649</t>
+          <t>126972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125474</t>
+          <t>124144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155076</t>
+          <t>155350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237495</t>
+          <t>235831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275353</t>
+          <t>274917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27866</t>
+          <t>28469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48684</t>
+          <t>49025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54507</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>90688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141543</t>
+          <t>140586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166789</t>
+          <t>168989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135563</t>
+          <t>135222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156381</t>
+          <t>155778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285194</t>
+          <t>283960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320141</t>
+          <t>317246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>44812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65686</t>
+          <t>65659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45954</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>67674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95477</t>
+          <t>96143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126732</t>
+          <t>125620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102276</t>
+          <t>102303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123521</t>
+          <t>123150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112281</t>
+          <t>112328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134048</t>
+          <t>134263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221233</t>
+          <t>222345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252488</t>
+          <t>251822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174745</t>
+          <t>176846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229342</t>
+          <t>228486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236671</t>
+          <t>234238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>291279</t>
+          <t>289888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>428080</t>
+          <t>426337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505781</t>
+          <t>506888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434217</t>
+          <t>435073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>488814</t>
+          <t>486713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>468036</t>
+          <t>469427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>522644</t>
+          <t>525077</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>917093</t>
+          <t>915986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>994794</t>
+          <t>996537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33035</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25487</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41723</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29231</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22515</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37674</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22584</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37453</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33035</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>25238</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41882</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52278</t>
+          <t>51797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74027</t>
+          <t>73070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85254</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76566</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>92802</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75978</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67535</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>82694</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67756</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85254</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76407</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>93051</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149472</t>
+          <t>150429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171221</t>
+          <t>171702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41248</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33165</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49818</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>37650</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29976</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44970</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30163</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,13%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>41248</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>33067</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>50076</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,31%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>67768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90371</t>
+          <t>90300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>99494</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90924</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>107577</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>87315</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94989</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>78558</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>94802</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,87%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>99494</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>90666</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>107675</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,69%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175336</t>
+          <t>175407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198121</t>
+          <t>197939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>34566</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27474</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42757</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>31591</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24929</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39236</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24825</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39310</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>34566</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27803</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>42940</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56655</t>
+          <t>56080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77428</t>
+          <t>77222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78007</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85099</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>76257</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>68612</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>82919</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68538</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>83023</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78007</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69633</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>84770</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>69,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142992</t>
+          <t>143198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163765</t>
+          <t>164340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51190</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42182</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61055</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>60623</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49505</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>70963</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50522</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>70612</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>36,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51190</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>42001</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61083</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97948</t>
+          <t>97022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127826</t>
+          <t>126144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105756</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95891</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>114764</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>94373</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>115831</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>94724</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>114814</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>63,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105756</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95863</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>114945</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194456</t>
+          <t>196138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224334</t>
+          <t>225260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>142875</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177263</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33,54%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>159096</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>143346</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>175521</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>141828</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>176193</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>145465</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>180130</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>295036</t>
+          <t>293215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343331</t>
+          <t>342599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>368511</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>351286</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>385674</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>69,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>66,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>72,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>344263</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>327838</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>360013</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>327166</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>361531</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>368511</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>348419</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>383084</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688577</t>
+          <t>689309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736872</t>
+          <t>738693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>99042</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>92818</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>103766</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>82,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>79746</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>72833</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85248</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>72814</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>85238</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>82,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>74,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>99042</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>92607</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>103834</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168700</t>
+          <t>169749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186267</t>
+          <t>186333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12828</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8104</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19052</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17383</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11881</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24296</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11891</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24315</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,9%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12828</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8036</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19263</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22732</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40299</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>111870</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>111870</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>111870</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>111870</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>111870</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>111870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125544</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116531</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>132447</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>106485</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>98474</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>113157</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>98951</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>112910</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>82,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>125544</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>116961</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>132189</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221725</t>
+          <t>221269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242317</t>
+          <t>242763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29012</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22109</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38025</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22498</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15826</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30509</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16073</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30032</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>17,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>29012</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22367</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37595</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41222</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>62270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>101377</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94622</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106913</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>87969</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81427</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93161</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>81423</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>93778</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>83,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>77,66%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>101377</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>95512</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>107073</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>81,79%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179545</t>
+          <t>179546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197218</t>
+          <t>196994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15407</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9871</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22162</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16882</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11690</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23424</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11073</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23428</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>16,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>22,34%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>15407</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9711</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21272</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>49</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42089</t>
+          <t>42088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>123837</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>114966</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>131289</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>74,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>119606</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>111121</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>127268</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>110974</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>126718</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>81,92%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>123837</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>115268</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>131117</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>79,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231827</t>
+          <t>231204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254307</t>
+          <t>253852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31104</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23652</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39975</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>26396</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18734</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34881</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19284</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35028</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>18,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>31104</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23824</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39673</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46636</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>69739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>436342</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>464031</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>569</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>380002</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>407906</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>379722</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>407139</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>449801</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>436171</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>462974</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822566</t>
+          <t>824311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>861399</t>
+          <t>862397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>88350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>74120</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>101809</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>83159</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>69059</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>96963</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>69826</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>97243</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>17,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>88350</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>75177</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>101980</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153716</t>
+          <t>152718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>190804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>76624</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66927</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>82663</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>75,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>65,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>61396</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54040</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>68227</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53277</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>67880</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>70,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>76624</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>67472</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83382</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128183</t>
+          <t>127160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147422</t>
+          <t>147391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25172</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19133</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34869</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25822</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18991</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>33178</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33941</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25172</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18414</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34324</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>41622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>61853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>101796</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>101796</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>101796</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87218</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87218</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87218</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>101796</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>101796</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>101796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>135624</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125595</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>143433</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>105027</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>95208</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>113328</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>95595</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>112929</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>70,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>135624</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>126332</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>143079</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>78,32%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>226948</t>
+          <t>227166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252883</t>
+          <t>252485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37538</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29729</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47567</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>44407</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36106</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>54226</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>36505</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53839</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37538</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30083</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>46830</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69713</t>
+          <t>70111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95648</t>
+          <t>95430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>173162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>173162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>173162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149434</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149434</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149434</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>173162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>173162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>173162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70101</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61040</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>79390</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>63329</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54816</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71486</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>54425</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>70698</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>60115</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>78904</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121300</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144959</t>
+          <t>147198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,96%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61359</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52070</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70420</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>53,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>50715</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42558</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>59228</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>43346</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>59619</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61359</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52556</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>71345</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100545</t>
+          <t>98306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124204</t>
+          <t>124304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>131460</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>131460</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>131460</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>114044</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>114044</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>114044</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>131460</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>131460</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>131460</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>109324</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>99525</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>118774</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>64,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>121194</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>111227</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>130639</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>110903</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>130512</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>109324</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>99791</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>118350</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>70,39%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217730</t>
+          <t>216463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244657</t>
+          <t>242756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45989</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36539</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55788</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>44135</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34690</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54102</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>34817</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>54426</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>45989</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36963</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>55522</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>29,61%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75986</t>
+          <t>77887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102913</t>
+          <t>104180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>155313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>155313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>155313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>165329</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165329</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165329</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>155313</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>155313</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>155313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>372627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>408700</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>66,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>334612</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>370677</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>333199</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>367020</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>64,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>391673</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>373103</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>409824</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>718387</t>
+          <t>719347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>767403</t>
+          <t>766056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -6107,67 +6107,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>170058</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>153031</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>189104</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>165080</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>145348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>181413</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>149005</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>182826</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,99%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>170058</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>151907</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>188628</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310353</t>
+          <t>311700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359369</t>
+          <t>358409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>776</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>516025</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>516025</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>516025</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49199</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38473</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67407</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40503</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31886</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49230</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53057</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73718</t>
+          <t>50488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>93560</t>
+          <t>90958</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115529</t>
+          <t>108944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76707</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58499</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>87433</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>46,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>76398</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67671</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85015</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87355</t>
+          <t>78986</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66694</t>
+          <t>70257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100760</t>
+          <t>87627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>163753</t>
+          <t>155693</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141784</t>
+          <t>137707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178610</t>
+          <t>169206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>120745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257313</t>
+          <t>246651</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257313</t>
+          <t>246651</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257313</t>
+          <t>246651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>109281</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>95630</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125246</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>72867</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>61324</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>87340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>46,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>114494</t>
+          <t>67804</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99303</t>
+          <t>56132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130509</t>
+          <t>79833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>187360</t>
+          <t>177086</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>168032</t>
+          <t>158687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207118</t>
+          <t>194123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>127637</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>111672</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>141288</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>53,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>115429</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100956</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126972</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>61,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140159</t>
+          <t>114734</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124144</t>
+          <t>102705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155350</t>
+          <t>126406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>255589</t>
+          <t>242371</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235831</t>
+          <t>225334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274917</t>
+          <t>260770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236918</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236918</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236918</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>188296</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>188296</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>188296</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254653</t>
+          <t>182538</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254653</t>
+          <t>182538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254653</t>
+          <t>182538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>442949</t>
+          <t>419457</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>442949</t>
+          <t>419457</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>442949</t>
+          <t>419457</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34767</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26741</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44282</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37089</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21412</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49815</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28469</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49025</t>
+          <t>46197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74175</t>
+          <t>71765</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57402</t>
+          <t>60537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90688</t>
+          <t>86693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132603</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>123088</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140629</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>153312</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140586</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168989</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>147161</t>
+          <t>120052</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135222</t>
+          <t>110853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155778</t>
+          <t>129081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>300473</t>
+          <t>252655</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283960</t>
+          <t>237727</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317246</t>
+          <t>263883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167370</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167370</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167370</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184247</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184247</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184247</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374648</t>
+          <t>324420</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374648</t>
+          <t>324420</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374648</t>
+          <t>324420</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54006</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43741</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65478</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54225</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>44812</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65659</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45739</t>
+          <t>45609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67674</t>
+          <t>67295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96143</t>
+          <t>95793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125620</t>
+          <t>124962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>114222</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>102750</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>124487</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>113737</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>102303</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>123150</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67,72%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123504</t>
+          <t>111812</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112328</t>
+          <t>99850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134263</t>
+          <t>121536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>237241</t>
+          <t>226033</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>222345</t>
+          <t>210411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251822</t>
+          <t>239580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180002</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180002</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180002</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>347965</t>
+          <t>335373</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>347965</t>
+          <t>335373</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>347965</t>
+          <t>335373</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>247254</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>223101</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>272696</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>204684</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>176846</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>228486</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>261135</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234238</t>
+          <t>181945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289888</t>
+          <t>221074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>449149</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426337</t>
+          <t>416526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506888</t>
+          <t>483894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>451169</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>425727</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>475322</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>458875</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>435073</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>486713</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>69,15%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>498180</t>
+          <t>425583</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469427</t>
+          <t>406404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525077</t>
+          <t>445533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>957055</t>
+          <t>876752</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>915986</t>
+          <t>842007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>996537</t>
+          <t>909375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663559</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663559</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663559</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>627478</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>627478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>627478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1422874</t>
+          <t>1325901</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1422874</t>
+          <t>1325901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1422874</t>
+          <t>1325901</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
